--- a/chapter3/input/chapter3_demo_data.xlsx
+++ b/chapter3/input/chapter3_demo_data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A49443-8B2A-4698-AA1E-0F8D093A24D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226190FC-9C22-46A0-8E95-41A4F5DFD9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="4860" windowWidth="28800" windowHeight="15410" activeTab="6" xr2:uid="{AFFCA931-CB2A-4AED-B7E5-2638B5FCE6AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{AFFCA931-CB2A-4AED-B7E5-2638B5FCE6AD}"/>
   </bookViews>
   <sheets>
     <sheet name="初期データ" sheetId="2" r:id="rId1"/>
@@ -1181,6 +1181,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1197,24 +1215,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2604,28 +2604,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29A7775-745C-46D9-8F8E-94D6562DAC1D}">
   <dimension ref="B5:AJ36"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="19.9140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.9140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="19.9375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.9375" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="18.6875" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.3125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="45.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="29" width="41.58203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="45.1875" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="41.5625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="51.6875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="49.6875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="49.1875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="48" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="49.1640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="51.4140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="49.6875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="49.1875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="51.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C5" s="11" t="s">
         <v>50</v>
       </c>
@@ -2729,109 +2729,109 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="75">
         <v>45310</v>
       </c>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="81">
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="75">
         <v>45321</v>
       </c>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82">
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76">
         <v>45329</v>
       </c>
-      <c r="P6" s="82"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="81">
+      <c r="P6" s="76"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="75">
         <v>45337</v>
       </c>
-      <c r="S6" s="82"/>
-      <c r="T6" s="82"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="81">
+      <c r="S6" s="76"/>
+      <c r="T6" s="76"/>
+      <c r="U6" s="77"/>
+      <c r="V6" s="75">
         <v>45350</v>
       </c>
-      <c r="W6" s="82"/>
-      <c r="X6" s="82"/>
-      <c r="Y6" s="83"/>
-      <c r="Z6" s="81">
+      <c r="W6" s="76"/>
+      <c r="X6" s="76"/>
+      <c r="Y6" s="77"/>
+      <c r="Z6" s="75">
         <v>45366</v>
       </c>
-      <c r="AA6" s="82"/>
-      <c r="AB6" s="82"/>
-      <c r="AC6" s="83"/>
-      <c r="AD6" s="81">
+      <c r="AA6" s="76"/>
+      <c r="AB6" s="76"/>
+      <c r="AC6" s="77"/>
+      <c r="AD6" s="75">
         <v>45392</v>
       </c>
-      <c r="AE6" s="82"/>
-      <c r="AF6" s="82"/>
-      <c r="AG6" s="82"/>
-      <c r="AH6" s="82"/>
-      <c r="AI6" s="82"/>
-      <c r="AJ6" s="83"/>
-    </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="76"/>
+      <c r="AH6" s="76"/>
+      <c r="AI6" s="76"/>
+      <c r="AJ6" s="77"/>
+    </row>
+    <row r="7" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="84" t="s">
+      <c r="D7" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="86"/>
-      <c r="R7" s="84" t="s">
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="86"/>
-      <c r="V7" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="W7" s="85"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="86"/>
-      <c r="Z7" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA7" s="85"/>
-      <c r="AB7" s="85"/>
-      <c r="AC7" s="86"/>
-      <c r="AD7" s="84" t="s">
+      <c r="S7" s="79"/>
+      <c r="T7" s="79"/>
+      <c r="U7" s="80"/>
+      <c r="V7" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="W7" s="79"/>
+      <c r="X7" s="79"/>
+      <c r="Y7" s="80"/>
+      <c r="Z7" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA7" s="79"/>
+      <c r="AB7" s="79"/>
+      <c r="AC7" s="80"/>
+      <c r="AD7" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="85"/>
-      <c r="AF7" s="85"/>
-      <c r="AG7" s="85"/>
-      <c r="AH7" s="85"/>
-      <c r="AI7" s="85"/>
-      <c r="AJ7" s="86"/>
-    </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+      <c r="AE7" s="79"/>
+      <c r="AF7" s="79"/>
+      <c r="AG7" s="79"/>
+      <c r="AH7" s="79"/>
+      <c r="AI7" s="79"/>
+      <c r="AJ7" s="80"/>
+    </row>
+    <row r="8" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
@@ -2875,7 +2875,7 @@
       <c r="AI8" s="2"/>
       <c r="AJ8" s="2"/>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B9" s="20" t="s">
         <v>51</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B10" s="21"/>
       <c r="C10" s="1" t="s">
         <v>96</v>
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B11" s="21"/>
       <c r="C11" s="1" t="s">
         <v>97</v>
@@ -3192,7 +3192,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B12" s="21"/>
       <c r="C12" s="1" t="s">
         <v>98</v>
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B13" s="21"/>
       <c r="C13" s="1" t="s">
         <v>99</v>
@@ -3402,7 +3402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B14" s="21"/>
       <c r="C14" s="1" t="s">
         <v>100</v>
@@ -3507,7 +3507,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B15" s="21"/>
       <c r="C15" s="1" t="s">
         <v>101</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B16" s="21"/>
       <c r="C16" s="1" t="s">
         <v>102</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B17" s="21"/>
       <c r="C17" s="1" t="s">
         <v>103</v>
@@ -3822,7 +3822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B18" s="21"/>
       <c r="C18" s="1" t="s">
         <v>104</v>
@@ -3927,7 +3927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B19" s="21"/>
       <c r="C19" s="1" t="s">
         <v>105</v>
@@ -4032,7 +4032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B20" s="21"/>
       <c r="C20" s="1" t="s">
         <v>106</v>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B21" s="22"/>
       <c r="C21" s="1" t="s">
         <v>107</v>
@@ -4242,7 +4242,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C22" s="9"/>
       <c r="D22" s="43"/>
       <c r="E22" s="43"/>
@@ -4275,7 +4275,7 @@
       <c r="AF22" s="43"/>
       <c r="AG22" s="43"/>
     </row>
-    <row r="23" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B23" s="20" t="s">
         <v>52</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B24" s="21"/>
       <c r="C24" s="1" t="s">
         <v>8</v>
@@ -4487,39 +4487,39 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:36" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:36" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B25" s="16"/>
       <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="76"/>
-      <c r="P25" s="76"/>
-      <c r="Q25" s="76"/>
-      <c r="R25" s="76"/>
-      <c r="S25" s="76"/>
-      <c r="T25" s="76"/>
-      <c r="U25" s="76"/>
-      <c r="V25" s="76"/>
-      <c r="W25" s="76"/>
-      <c r="X25" s="76"/>
-      <c r="Y25" s="76"/>
-      <c r="Z25" s="76"/>
-      <c r="AA25" s="76"/>
-      <c r="AB25" s="76"/>
-      <c r="AC25" s="77"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="82"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="82"/>
+      <c r="AB25" s="82"/>
+      <c r="AC25" s="83"/>
       <c r="AD25" s="8">
         <v>9.8199999999999985</v>
       </c>
@@ -4542,10 +4542,10 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C26" s="9"/>
     </row>
-    <row r="27" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B27" s="20" t="s">
         <v>54</v>
       </c>
@@ -4652,70 +4652,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B28" s="21"/>
       <c r="C28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="78" t="s">
+      <c r="D28" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="79"/>
-      <c r="Q28" s="80"/>
-      <c r="R28" s="78" t="s">
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
+      <c r="I28" s="85"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="S28" s="79"/>
-      <c r="T28" s="79"/>
-      <c r="U28" s="79"/>
-      <c r="V28" s="79"/>
-      <c r="W28" s="79"/>
-      <c r="X28" s="79"/>
-      <c r="Y28" s="79"/>
-      <c r="Z28" s="79"/>
-      <c r="AA28" s="79"/>
-      <c r="AB28" s="79"/>
-      <c r="AC28" s="79"/>
-      <c r="AD28" s="79"/>
-      <c r="AE28" s="79"/>
-      <c r="AF28" s="79"/>
-      <c r="AG28" s="79"/>
-      <c r="AH28" s="79"/>
-      <c r="AI28" s="79"/>
-      <c r="AJ28" s="80"/>
-    </row>
-    <row r="29" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+      <c r="S28" s="85"/>
+      <c r="T28" s="85"/>
+      <c r="U28" s="85"/>
+      <c r="V28" s="85"/>
+      <c r="W28" s="85"/>
+      <c r="X28" s="85"/>
+      <c r="Y28" s="85"/>
+      <c r="Z28" s="85"/>
+      <c r="AA28" s="85"/>
+      <c r="AB28" s="85"/>
+      <c r="AC28" s="85"/>
+      <c r="AD28" s="85"/>
+      <c r="AE28" s="85"/>
+      <c r="AF28" s="85"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="85"/>
+      <c r="AJ28" s="86"/>
+    </row>
+    <row r="29" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B29" s="21"/>
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="80"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="86"/>
       <c r="R29" s="47">
         <v>100</v>
       </c>
@@ -4774,27 +4774,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B30" s="22"/>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="78" t="s">
+      <c r="D30" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="79"/>
-      <c r="P30" s="79"/>
-      <c r="Q30" s="80"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="85"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="86"/>
       <c r="R30" s="47">
         <v>0.01</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B31" s="10"/>
       <c r="C31" s="9"/>
       <c r="D31" s="44"/>
@@ -4887,7 +4887,7 @@
       <c r="AF31" s="44"/>
       <c r="AG31" s="44"/>
     </row>
-    <row r="32" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B32" s="20" t="s">
         <v>53</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B33" s="22"/>
       <c r="C33" s="1" t="s">
         <v>5</v>
@@ -5099,7 +5099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -5132,7 +5132,7 @@
       <c r="AF34" s="9"/>
       <c r="AG34" s="9"/>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B35" s="20" t="s">
         <v>55</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B36" s="22"/>
       <c r="C36" s="1" t="s">
         <v>6</v>
@@ -5346,6 +5346,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D25:AC25"/>
+    <mergeCell ref="D30:Q30"/>
+    <mergeCell ref="D29:Q29"/>
+    <mergeCell ref="D28:Q28"/>
+    <mergeCell ref="R28:AJ28"/>
+    <mergeCell ref="V6:Y6"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="AD6:AJ6"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="AD7:AJ7"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="R6:U6"/>
     <mergeCell ref="D7:H7"/>
@@ -5353,17 +5364,6 @@
     <mergeCell ref="R7:U7"/>
     <mergeCell ref="I6:N6"/>
     <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="AD6:AJ6"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="AD7:AJ7"/>
-    <mergeCell ref="D25:AC25"/>
-    <mergeCell ref="D30:Q30"/>
-    <mergeCell ref="D29:Q29"/>
-    <mergeCell ref="D28:Q28"/>
-    <mergeCell ref="R28:AJ28"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5374,28 +5374,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75195F36-03CC-44EA-84BC-A1B71C21604F}">
   <dimension ref="B5:AJ36"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.4140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="42.58203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="29" width="39.08203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="48.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="46.1640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="45.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="46.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="46.1640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="48.4140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="19.3125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.4375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="19.3125" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="18.1875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="25.8125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.6875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.8125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="42.5625" bestFit="1" customWidth="1"/>
+    <col min="23" max="29" width="39.0625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="48.6875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="46.6875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="46.1875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="45.1875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="46.6875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="46.1875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="48.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C5" s="11" t="s">
         <v>50</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C6" s="1" t="s">
         <v>135</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
@@ -5751,7 +5751,7 @@
       <c r="AI8" s="2"/>
       <c r="AJ8" s="2"/>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B9" s="20" t="s">
         <v>51</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B10" s="21"/>
       <c r="C10" s="1" t="s">
         <v>96</v>
@@ -5963,7 +5963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B11" s="21"/>
       <c r="C11" s="1" t="s">
         <v>97</v>
@@ -6068,7 +6068,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B12" s="21"/>
       <c r="C12" s="1" t="s">
         <v>98</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B13" s="21"/>
       <c r="C13" s="1" t="s">
         <v>99</v>
@@ -6278,7 +6278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B14" s="21"/>
       <c r="C14" s="1" t="s">
         <v>100</v>
@@ -6383,7 +6383,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B15" s="21"/>
       <c r="C15" s="1" t="s">
         <v>101</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B16" s="21"/>
       <c r="C16" s="1" t="s">
         <v>102</v>
@@ -6593,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B17" s="21"/>
       <c r="C17" s="1" t="s">
         <v>103</v>
@@ -6698,7 +6698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B18" s="21"/>
       <c r="C18" s="1" t="s">
         <v>104</v>
@@ -6803,7 +6803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B19" s="21"/>
       <c r="C19" s="1" t="s">
         <v>105</v>
@@ -6908,7 +6908,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B20" s="21"/>
       <c r="C20" s="1" t="s">
         <v>106</v>
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B21" s="22"/>
       <c r="C21" s="1" t="s">
         <v>107</v>
@@ -7118,7 +7118,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C22" s="9"/>
       <c r="D22" s="43"/>
       <c r="E22" s="43"/>
@@ -7151,7 +7151,7 @@
       <c r="AF22" s="43"/>
       <c r="AG22" s="43"/>
     </row>
-    <row r="23" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B23" s="20" t="s">
         <v>52</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B24" s="21"/>
       <c r="C24" s="1" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:36" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:36" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B25" s="16"/>
       <c r="C25" s="1" t="s">
         <v>9</v>
@@ -7468,10 +7468,10 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C26" s="9"/>
     </row>
-    <row r="27" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B27" s="20" t="s">
         <v>54</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B28" s="21"/>
       <c r="C28" s="1" t="s">
         <v>1</v>
@@ -7683,7 +7683,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B29" s="21"/>
       <c r="C29" s="1" t="s">
         <v>2</v>
@@ -7788,7 +7788,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B30" s="22"/>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -7893,7 +7893,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B31" s="10"/>
       <c r="C31" s="9"/>
       <c r="D31" s="44"/>
@@ -7927,7 +7927,7 @@
       <c r="AF31" s="44"/>
       <c r="AG31" s="44"/>
     </row>
-    <row r="32" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B32" s="20" t="s">
         <v>53</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B33" s="22"/>
       <c r="C33" s="1" t="s">
         <v>5</v>
@@ -8139,7 +8139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.7">
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -8172,7 +8172,7 @@
       <c r="AF34" s="9"/>
       <c r="AG34" s="9"/>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B35" s="20" t="s">
         <v>55</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:36" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B36" s="22"/>
       <c r="C36" s="1" t="s">
         <v>6</v>
@@ -8394,27 +8394,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B744582-CF08-477A-A386-996EB0CCB24C}">
   <dimension ref="B5:AC39"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.0625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.8125" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="6.6875" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.8125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.4375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.3125" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="8.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.5" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:29" x14ac:dyDescent="0.7">
       <c r="F5" s="18" t="s">
         <v>51</v>
       </c>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC5" s="19"/>
     </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B6" s="23" t="s">
         <v>50</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B8" s="23" t="s">
         <v>12</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B10" s="23" t="s">
         <v>14</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B11" s="23" t="s">
         <v>15</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B13" s="23" t="s">
         <v>17</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B14" s="23" t="s">
         <v>18</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B15" s="23" t="s">
         <v>19</v>
       </c>
@@ -9294,7 +9294,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B16" s="23" t="s">
         <v>20</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B17" s="23" t="s">
         <v>21</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B18" s="23" t="s">
         <v>22</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B19" s="23" t="s">
         <v>23</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B20" s="23" t="s">
         <v>24</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B21" s="23" t="s">
         <v>25</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B22" s="23" t="s">
         <v>26</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B23" s="23" t="s">
         <v>27</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B24" s="23" t="s">
         <v>28</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B25" s="23" t="s">
         <v>29</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B26" s="23" t="s">
         <v>30</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B27" s="23" t="s">
         <v>31</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B28" s="23" t="s">
         <v>32</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B29" s="23" t="s">
         <v>33</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B30" s="23" t="s">
         <v>34</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B31" s="23" t="s">
         <v>35</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B32" s="23" t="s">
         <v>43</v>
       </c>
@@ -10724,7 +10724,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B33" s="23" t="s">
         <v>44</v>
       </c>
@@ -10810,7 +10810,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="34" spans="2:29" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:29" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B34" s="23" t="s">
         <v>45</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="35" spans="2:29" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:29" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B35" s="23" t="s">
         <v>46</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B36" s="23" t="s">
         <v>62</v>
       </c>
@@ -11062,7 +11062,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="37" spans="2:29" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:29" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B37" s="11" t="s">
         <v>71</v>
       </c>
@@ -11146,7 +11146,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="38" spans="2:29" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:29" ht="35.25" x14ac:dyDescent="0.7">
       <c r="B38" s="11" t="s">
         <v>72</v>
       </c>
@@ -11230,7 +11230,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.7">
       <c r="B39" s="11" t="s">
         <v>73</v>
       </c>
@@ -11324,28 +11324,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D727E699-FD26-449C-905C-CDD90899F4AB}">
   <dimension ref="B5:AD39"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.0625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.8125" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="6.6875" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.8125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.33203125" customWidth="1"/>
+    <col min="21" max="21" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.3125" customWidth="1"/>
     <col min="23" max="23" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.4375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.3125" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="8.5" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.5" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:30" x14ac:dyDescent="0.7">
       <c r="F5" s="18" t="s">
         <v>51</v>
       </c>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="AD5" s="19"/>
     </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B6" s="23" t="s">
         <v>50</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
@@ -11556,7 +11556,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B8" s="23" t="s">
         <v>12</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B9" s="23" t="s">
         <v>13</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B10" s="23" t="s">
         <v>14</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B11" s="23" t="s">
         <v>15</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B13" s="23" t="s">
         <v>17</v>
       </c>
@@ -12068,7 +12068,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B14" s="23" t="s">
         <v>18</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B15" s="23" t="s">
         <v>19</v>
       </c>
@@ -12238,7 +12238,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B16" s="23" t="s">
         <v>20</v>
       </c>
@@ -12323,7 +12323,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="17" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B17" s="23" t="s">
         <v>21</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="18" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B18" s="23" t="s">
         <v>22</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="19" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B19" s="23" t="s">
         <v>23</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B20" s="23" t="s">
         <v>24</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B21" s="23" t="s">
         <v>25</v>
       </c>
@@ -12748,7 +12748,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="22" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B22" s="23" t="s">
         <v>26</v>
       </c>
@@ -12833,7 +12833,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="23" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B23" s="23" t="s">
         <v>27</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="24" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B24" s="23" t="s">
         <v>28</v>
       </c>
@@ -13003,7 +13003,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="25" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B25" s="23" t="s">
         <v>29</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B26" s="23" t="s">
         <v>30</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B27" s="23" t="s">
         <v>31</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B28" s="23" t="s">
         <v>32</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="29" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B29" s="23" t="s">
         <v>33</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B30" s="23" t="s">
         <v>34</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B31" s="23" t="s">
         <v>35</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B32" s="23" t="s">
         <v>43</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B33" s="23" t="s">
         <v>44</v>
       </c>
@@ -13774,7 +13774,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B34" s="23" t="s">
         <v>45</v>
       </c>
@@ -13861,7 +13861,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B35" s="23" t="s">
         <v>46</v>
       </c>
@@ -13948,7 +13948,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B36" s="23" t="s">
         <v>62</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B37" s="11" t="s">
         <v>71</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B38" s="11" t="s">
         <v>72</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B39" s="11" t="s">
         <v>73</v>
       </c>
@@ -14306,24 +14306,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC155531-539F-473A-BEFE-FAB0C4C3EE43}">
   <dimension ref="B4:AD39"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="2" max="2" width="11.9140625" customWidth="1"/>
-    <col min="3" max="3" width="15.4140625" customWidth="1"/>
-    <col min="4" max="4" width="8.08203125" customWidth="1"/>
-    <col min="5" max="5" width="7.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="8.9140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.08203125" customWidth="1"/>
-    <col min="20" max="24" width="9.9140625" customWidth="1"/>
+    <col min="2" max="2" width="11.9375" customWidth="1"/>
+    <col min="3" max="3" width="15.4375" customWidth="1"/>
+    <col min="4" max="4" width="8.0625" customWidth="1"/>
+    <col min="5" max="5" width="7.0625" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="8.9375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="10.6875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.0625" customWidth="1"/>
+    <col min="20" max="24" width="9.9375" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="26" width="13.5" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.9140625" customWidth="1"/>
-    <col min="29" max="30" width="11.6640625" customWidth="1"/>
+    <col min="28" max="28" width="9.9375" customWidth="1"/>
+    <col min="29" max="30" width="11.6875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:30" ht="90" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:30" ht="88.15" x14ac:dyDescent="0.7">
       <c r="T4" s="3" t="s">
         <v>119</v>
       </c>
@@ -14346,7 +14346,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:30" x14ac:dyDescent="0.7">
       <c r="F5" s="18" t="s">
         <v>51</v>
       </c>
@@ -14383,7 +14383,7 @@
       <c r="AC5" s="9"/>
       <c r="AD5" s="19"/>
     </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B6" s="61" t="s">
         <v>50</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B7" s="58" t="s">
         <v>10</v>
       </c>
@@ -14553,7 +14553,7 @@
       <c r="AC7" s="27"/>
       <c r="AD7" s="60"/>
     </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B8" s="58" t="s">
         <v>12</v>
       </c>
@@ -14634,7 +14634,7 @@
       <c r="AC8" s="27"/>
       <c r="AD8" s="60"/>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B9" s="58" t="s">
         <v>13</v>
       </c>
@@ -14715,7 +14715,7 @@
       <c r="AC9" s="27"/>
       <c r="AD9" s="60"/>
     </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B10" s="58" t="s">
         <v>14</v>
       </c>
@@ -14796,7 +14796,7 @@
       <c r="AC10" s="27"/>
       <c r="AD10" s="60"/>
     </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B11" s="58" t="s">
         <v>15</v>
       </c>
@@ -14877,7 +14877,7 @@
       <c r="AC11" s="27"/>
       <c r="AD11" s="60"/>
     </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B12" s="58" t="s">
         <v>16</v>
       </c>
@@ -14960,7 +14960,7 @@
       <c r="AC12" s="27"/>
       <c r="AD12" s="60"/>
     </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B13" s="58" t="s">
         <v>17</v>
       </c>
@@ -15041,7 +15041,7 @@
       <c r="AC13" s="27"/>
       <c r="AD13" s="60"/>
     </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B14" s="58" t="s">
         <v>18</v>
       </c>
@@ -15122,7 +15122,7 @@
       <c r="AC14" s="27"/>
       <c r="AD14" s="60"/>
     </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B15" s="58" t="s">
         <v>19</v>
       </c>
@@ -15203,7 +15203,7 @@
       <c r="AC15" s="27"/>
       <c r="AD15" s="60"/>
     </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B16" s="58" t="s">
         <v>20</v>
       </c>
@@ -15284,7 +15284,7 @@
       <c r="AC16" s="27"/>
       <c r="AD16" s="60"/>
     </row>
-    <row r="17" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B17" s="58" t="s">
         <v>21</v>
       </c>
@@ -15365,7 +15365,7 @@
       <c r="AC17" s="27"/>
       <c r="AD17" s="60"/>
     </row>
-    <row r="18" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B18" s="58" t="s">
         <v>22</v>
       </c>
@@ -15446,7 +15446,7 @@
       <c r="AC18" s="27"/>
       <c r="AD18" s="60"/>
     </row>
-    <row r="19" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B19" s="58" t="s">
         <v>23</v>
       </c>
@@ -15527,7 +15527,7 @@
       <c r="AC19" s="27"/>
       <c r="AD19" s="60"/>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B20" s="58" t="s">
         <v>24</v>
       </c>
@@ -15608,7 +15608,7 @@
       <c r="AC20" s="27"/>
       <c r="AD20" s="60"/>
     </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B21" s="58" t="s">
         <v>25</v>
       </c>
@@ -15691,7 +15691,7 @@
       <c r="AC21" s="27"/>
       <c r="AD21" s="60"/>
     </row>
-    <row r="22" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B22" s="58" t="s">
         <v>26</v>
       </c>
@@ -15774,7 +15774,7 @@
       <c r="AC22" s="27"/>
       <c r="AD22" s="60"/>
     </row>
-    <row r="23" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B23" s="58" t="s">
         <v>27</v>
       </c>
@@ -15857,7 +15857,7 @@
       <c r="AC23" s="27"/>
       <c r="AD23" s="60"/>
     </row>
-    <row r="24" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B24" s="58" t="s">
         <v>28</v>
       </c>
@@ -15940,7 +15940,7 @@
       <c r="AC24" s="27"/>
       <c r="AD24" s="60"/>
     </row>
-    <row r="25" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B25" s="58" t="s">
         <v>29</v>
       </c>
@@ -16025,7 +16025,7 @@
       <c r="AC25" s="27"/>
       <c r="AD25" s="60"/>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B26" s="58" t="s">
         <v>30</v>
       </c>
@@ -16108,7 +16108,7 @@
       <c r="AC26" s="27"/>
       <c r="AD26" s="60"/>
     </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B27" s="58" t="s">
         <v>31</v>
       </c>
@@ -16191,7 +16191,7 @@
       <c r="AC27" s="27"/>
       <c r="AD27" s="60"/>
     </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B28" s="58" t="s">
         <v>32</v>
       </c>
@@ -16274,7 +16274,7 @@
       <c r="AC28" s="27"/>
       <c r="AD28" s="60"/>
     </row>
-    <row r="29" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B29" s="58" t="s">
         <v>33</v>
       </c>
@@ -16357,7 +16357,7 @@
       <c r="AC29" s="27"/>
       <c r="AD29" s="60"/>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B30" s="58" t="s">
         <v>34</v>
       </c>
@@ -16440,7 +16440,7 @@
       <c r="AC30" s="27"/>
       <c r="AD30" s="60"/>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B31" s="58" t="s">
         <v>35</v>
       </c>
@@ -16523,7 +16523,7 @@
       <c r="AC31" s="27"/>
       <c r="AD31" s="60"/>
     </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B32" s="58" t="s">
         <v>43</v>
       </c>
@@ -16606,7 +16606,7 @@
       <c r="AC32" s="27"/>
       <c r="AD32" s="60"/>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B33" s="58" t="s">
         <v>44</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B34" s="58" t="s">
         <v>45</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B35" s="58" t="s">
         <v>46</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B36" s="58" t="s">
         <v>62</v>
       </c>
@@ -16956,7 +16956,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B37" s="59" t="s">
         <v>71</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B38" s="59" t="s">
         <v>72</v>
       </c>
@@ -17130,7 +17130,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.7">
       <c r="B39" s="64" t="s">
         <v>73</v>
       </c>
@@ -17230,9 +17230,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378FCD36-4939-467E-95CA-2D9070DB49FB}">
   <dimension ref="A1:Y25"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A1" s="74"/>
       <c r="B1" s="74" t="s">
         <v>121</v>
@@ -17307,7 +17307,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
         <v>122</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
         <v>123</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
         <v>124</v>
       </c>
@@ -17357,7 +17357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
         <v>126</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
         <v>127</v>
       </c>
@@ -17426,7 +17426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
         <v>128</v>
       </c>
@@ -17455,7 +17455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
         <v>129</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
         <v>130</v>
       </c>
@@ -17522,7 +17522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
         <v>131</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A13" t="s">
         <v>132</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
         <v>133</v>
       </c>
@@ -17645,7 +17645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -17795,7 +17795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -17851,7 +17851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -17910,7 +17910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -17972,7 +17972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A21" t="s">
         <v>134</v>
       </c>
@@ -18037,7 +18037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -18105,7 +18105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -18176,7 +18176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -18250,7 +18250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A25" s="73" t="s">
         <v>94</v>
       </c>
@@ -18349,27 +18349,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFD9269-7F18-4E64-8D48-3C1F1E4D91C0}">
   <dimension ref="B2:AF47"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="2" max="2" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.8125" customWidth="1"/>
+    <col min="5" max="5" width="4.8125" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="13" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="11" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.08203125" customWidth="1"/>
-    <col min="25" max="25" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.33203125" customWidth="1"/>
-    <col min="27" max="27" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.83203125" customWidth="1"/>
-    <col min="29" max="29" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.3125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.0625" customWidth="1"/>
+    <col min="25" max="25" width="14.3125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.3125" customWidth="1"/>
+    <col min="27" max="27" width="15.3125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.8125" customWidth="1"/>
+    <col min="29" max="29" width="6.8125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.3125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:32" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:32" ht="52.9" x14ac:dyDescent="0.7">
       <c r="V2" s="3" t="s">
         <v>49</v>
       </c>
@@ -18389,7 +18389,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:32" x14ac:dyDescent="0.7">
       <c r="F3" s="18" t="s">
         <v>51</v>
       </c>
@@ -18430,7 +18430,7 @@
       <c r="AE3" s="9"/>
       <c r="AF3" s="19"/>
     </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B5" s="41" t="s">
         <v>11</v>
       </c>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="AF5" s="41"/>
     </row>
-    <row r="6" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B6" s="41" t="s">
         <v>12</v>
       </c>
@@ -18719,7 +18719,7 @@
       </c>
       <c r="AF6" s="11"/>
     </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B7" s="41" t="s">
         <v>13</v>
       </c>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B8" s="41" t="s">
         <v>14</v>
       </c>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="AF8" s="41"/>
     </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B9" s="41" t="s">
         <v>15</v>
       </c>
@@ -19010,7 +19010,7 @@
       </c>
       <c r="AF9" s="1"/>
     </row>
-    <row r="10" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B10" s="41" t="s">
         <v>16</v>
       </c>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="AF10" s="11"/>
     </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B11" s="41" t="s">
         <v>17</v>
       </c>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="AF11" s="1"/>
     </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B12" s="41" t="s">
         <v>18</v>
       </c>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="AF12" s="1"/>
     </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B13" s="41" t="s">
         <v>19</v>
       </c>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="AF13" s="1"/>
     </row>
-    <row r="14" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B14" s="41" t="s">
         <v>20</v>
       </c>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="AF14" s="11"/>
     </row>
-    <row r="15" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B15" s="41" t="s">
         <v>21</v>
       </c>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="AF15" s="11"/>
     </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B16" s="41" t="s">
         <v>22</v>
       </c>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="AF16" s="1"/>
     </row>
-    <row r="17" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B17" s="41" t="s">
         <v>23</v>
       </c>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AF17" s="1"/>
     </row>
-    <row r="18" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B18" s="41" t="s">
         <v>24</v>
       </c>
@@ -19885,7 +19885,7 @@
       </c>
       <c r="AF18" s="1"/>
     </row>
-    <row r="19" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B19" s="41" t="s">
         <v>25</v>
       </c>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="AF19" s="1"/>
     </row>
-    <row r="20" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B20" s="41" t="s">
         <v>26</v>
       </c>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="AF20" s="11"/>
     </row>
-    <row r="21" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B21" s="41" t="s">
         <v>27</v>
       </c>
@@ -20176,7 +20176,7 @@
       </c>
       <c r="AF21" s="11"/>
     </row>
-    <row r="22" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B22" s="41" t="s">
         <v>28</v>
       </c>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AF22" s="11"/>
     </row>
-    <row r="23" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B23" s="41" t="s">
         <v>29</v>
       </c>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="AF23" s="11"/>
     </row>
-    <row r="24" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B24" s="41" t="s">
         <v>30</v>
       </c>
@@ -20469,7 +20469,7 @@
       </c>
       <c r="AF24" s="41"/>
     </row>
-    <row r="25" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B25" s="41" t="s">
         <v>31</v>
       </c>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B26" s="41" t="s">
         <v>32</v>
       </c>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="AF26" s="11"/>
     </row>
-    <row r="27" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B27" s="41" t="s">
         <v>33</v>
       </c>
@@ -20760,7 +20760,7 @@
       </c>
       <c r="AF27" s="11"/>
     </row>
-    <row r="28" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B28" s="41" t="s">
         <v>34</v>
       </c>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="AF28" s="41"/>
     </row>
-    <row r="29" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B29" s="41" t="s">
         <v>35</v>
       </c>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="AF29" s="41"/>
     </row>
-    <row r="30" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B30" s="41" t="s">
         <v>43</v>
       </c>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="AF30" s="41"/>
     </row>
-    <row r="31" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B31" s="41" t="s">
         <v>44</v>
       </c>
@@ -21152,7 +21152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B32" s="41" t="s">
         <v>45</v>
       </c>
@@ -21251,7 +21251,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B33" s="41" t="s">
         <v>46</v>
       </c>
@@ -21350,7 +21350,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B34" s="41" t="s">
         <v>62</v>
       </c>
@@ -21449,7 +21449,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B35" s="41" t="s">
         <v>71</v>
       </c>
@@ -21548,7 +21548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B36" s="41" t="s">
         <v>72</v>
       </c>
@@ -21647,7 +21647,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.7">
       <c r="B37" s="41" t="s">
         <v>74</v>
       </c>
@@ -21746,7 +21746,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B39" s="41" t="s">
         <v>108</v>
       </c>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="AF39" s="41"/>
     </row>
-    <row r="40" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B40" s="41" t="s">
         <v>109</v>
       </c>
@@ -21932,7 +21932,7 @@
       </c>
       <c r="AF40" s="41"/>
     </row>
-    <row r="41" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B41" s="41" t="s">
         <v>110</v>
       </c>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="AF41" s="41"/>
     </row>
-    <row r="42" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B42" s="11" t="s">
         <v>111</v>
       </c>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="AF42" s="11"/>
     </row>
-    <row r="43" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B43" s="11" t="s">
         <v>112</v>
       </c>
@@ -22211,7 +22211,7 @@
       </c>
       <c r="AF43" s="11"/>
     </row>
-    <row r="44" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:32" s="4" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B44" s="11" t="s">
         <v>113</v>
       </c>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="AF44" s="11"/>
     </row>
-    <row r="45" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B45" s="41" t="s">
         <v>115</v>
       </c>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="AF45" s="41"/>
     </row>
-    <row r="46" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B46" s="41" t="s">
         <v>116</v>
       </c>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="AF46" s="41"/>
     </row>
-    <row r="47" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:32" s="5" customFormat="1" x14ac:dyDescent="0.7">
       <c r="B47" s="41" t="s">
         <v>117</v>
       </c>
